--- a/execl/equip.xlsx
+++ b/execl/equip.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="25890" windowHeight="12375" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="equip" sheetId="2" r:id="rId1"/>
     <sheet name="equipAttr" sheetId="3" r:id="rId2"/>
     <sheet name="equipSkill" sheetId="4" r:id="rId3"/>
     <sheet name="equipSet" sheetId="5" r:id="rId4"/>
-    <sheet name="备注_功能&amp;表格关系说明" sheetId="1" r:id="rId5"/>
+    <sheet name="equipFusion" sheetId="6" r:id="rId5"/>
+    <sheet name="备注_功能&amp;表格关系说明" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="207">
   <si>
     <t>表格名称</t>
   </si>
@@ -570,6 +571,119 @@
   </si>
   <si>
     <t>sk_set01_5</t>
+  </si>
+  <si>
+    <t>装备融合表</t>
+  </si>
+  <si>
+    <t>必须3件装备才能融合。
+计算装备的加权点数</t>
+  </si>
+  <si>
+    <t>不填默认为0</t>
+  </si>
+  <si>
+    <t>装备品质对应点数
+1=白
+2=绿
+3=蓝
+4=紫
+5=橙
+6=红
+7=金</t>
+  </si>
+  <si>
+    <t>合成所需点数区间</t>
+  </si>
+  <si>
+    <t>白品权重</t>
+  </si>
+  <si>
+    <t>绿品权重</t>
+  </si>
+  <si>
+    <t>蓝品权重</t>
+  </si>
+  <si>
+    <t>紫品权重</t>
+  </si>
+  <si>
+    <t>橙品权重</t>
+  </si>
+  <si>
+    <t>ptsRange</t>
+  </si>
+  <si>
+    <t>wWhite</t>
+  </si>
+  <si>
+    <t>wGreen</t>
+  </si>
+  <si>
+    <t>wBlue</t>
+  </si>
+  <si>
+    <t>wPurple</t>
+  </si>
+  <si>
+    <t>wOrange</t>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
+  <si>
+    <t>Fusion01</t>
+  </si>
+  <si>
+    <t>0|3</t>
+  </si>
+  <si>
+    <t>权重区间1</t>
+  </si>
+  <si>
+    <t>Fusion02</t>
+  </si>
+  <si>
+    <t>3|5</t>
+  </si>
+  <si>
+    <t>权重区间2</t>
+  </si>
+  <si>
+    <t>Fusion03</t>
+  </si>
+  <si>
+    <t>6|8</t>
+  </si>
+  <si>
+    <t>权重区间3</t>
+  </si>
+  <si>
+    <t>Fusion04</t>
+  </si>
+  <si>
+    <t>9|11</t>
+  </si>
+  <si>
+    <t>权重区间4</t>
+  </si>
+  <si>
+    <t>Fusion05</t>
+  </si>
+  <si>
+    <t>12|14</t>
+  </si>
+  <si>
+    <t>权重区间5</t>
+  </si>
+  <si>
+    <t>Fusion06</t>
+  </si>
+  <si>
+    <t>15|999</t>
+  </si>
+  <si>
+    <t>权重区间6</t>
   </si>
   <si>
     <t>表格ID</t>
@@ -585,13 +699,31 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1110,192 +1242,215 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1613,615 +1768,615 @@
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="15.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.375" style="1" customWidth="1"/>
-    <col min="8" max="10" width="10.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="37.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="28.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.25" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="19.375" style="10" customWidth="1"/>
+    <col min="4" max="5" width="15.625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="20.375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="8.375" style="10" customWidth="1"/>
+    <col min="8" max="10" width="10.625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="37.5" style="10" customWidth="1"/>
+    <col min="12" max="12" width="28.25" style="10" customWidth="1"/>
+    <col min="13" max="13" width="16" style="10" customWidth="1"/>
+    <col min="14" max="14" width="12.625" style="10" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" ht="128.25" customHeight="1" spans="1:14">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="12" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="11"/>
+      <c r="F7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="11"/>
+      <c r="F8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="14">
         <v>1</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="6" t="s">
+      <c r="I9" s="14"/>
+      <c r="J9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="14">
         <v>2</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6" t="s">
+      <c r="I10" s="15"/>
+      <c r="J10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="14">
         <v>3</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6" t="s">
+      <c r="I11" s="15"/>
+      <c r="J11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="6"/>
+      <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="14">
         <v>4</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6" t="s">
+      <c r="I12" s="15"/>
+      <c r="J12" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="N12" s="6"/>
+      <c r="N12" s="15"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="15">
         <v>1</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6" t="s">
+      <c r="H13" s="15"/>
+      <c r="I13" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6" t="s">
+      <c r="J13" s="15"/>
+      <c r="K13" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6" t="s">
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="15">
         <v>1</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="s">
+      <c r="H14" s="15"/>
+      <c r="I14" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6" t="s">
+      <c r="J14" s="15"/>
+      <c r="K14" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6" t="s">
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="s">
+      <c r="H15" s="15"/>
+      <c r="I15" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6" t="s">
+      <c r="J15" s="15"/>
+      <c r="K15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6" t="s">
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="15">
         <v>1</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="s">
+      <c r="H16" s="15"/>
+      <c r="I16" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6" t="s">
+      <c r="J16" s="15"/>
+      <c r="K16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6" t="s">
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="15">
         <v>1</v>
       </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6" t="s">
+      <c r="H17" s="15"/>
+      <c r="I17" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6" t="s">
+      <c r="J17" s="15"/>
+      <c r="K17" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6" t="s">
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2238,381 +2393,381 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="7" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="7" customWidth="1"/>
-    <col min="5" max="5" width="16.75" style="7" customWidth="1"/>
-    <col min="6" max="7" width="12.875" style="7" customWidth="1"/>
-    <col min="8" max="16380" width="9" style="7" customWidth="1"/>
-    <col min="16381" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="13.75" style="16" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="16" customWidth="1"/>
+    <col min="5" max="5" width="16.75" style="16" customWidth="1"/>
+    <col min="6" max="7" width="12.875" style="16" customWidth="1"/>
+    <col min="8" max="16380" width="9" style="16" customWidth="1"/>
+    <col min="16381" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" ht="44" customHeight="1" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="9"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" ht="42.75" customHeight="1" spans="1:7">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="13"/>
+      <c r="G4" s="13" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="18" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:7">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="13" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="20">
         <v>1</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="25">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="20">
         <v>1</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="25">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="20">
         <v>1</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="20">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="20">
         <v>1</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="20">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="20">
         <v>1</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="20">
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="20">
         <v>2</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="25">
         <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="20">
         <v>2</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="25">
         <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="20">
         <v>2</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="20">
         <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="20">
         <v>2</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="20">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="20">
         <v>2</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="20">
         <v>50</v>
       </c>
     </row>
@@ -2629,698 +2784,698 @@
   <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26" style="1" customWidth="1"/>
-    <col min="3" max="5" width="15.25" style="7" customWidth="1"/>
-    <col min="6" max="6" width="18.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5" style="1" customWidth="1"/>
-    <col min="8" max="12" width="11.5" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="10" customWidth="1"/>
+    <col min="2" max="2" width="26" style="10" customWidth="1"/>
+    <col min="3" max="5" width="15.25" style="16" customWidth="1"/>
+    <col min="6" max="6" width="18.25" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="10" customWidth="1"/>
+    <col min="8" max="12" width="11.5" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" ht="99.75" spans="1:12">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="4" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="11"/>
+      <c r="G4" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="2" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9" t="s">
+      <c r="D6" s="19"/>
+      <c r="E6" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="11" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="9" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="3" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="22">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="15">
         <v>0</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="15">
         <v>1000</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="15">
         <v>500</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="15">
         <v>0</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="15">
         <v>0</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="22">
         <v>2</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="15">
         <v>0</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="15">
         <v>500</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="15">
         <v>1000</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="15">
         <v>200</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="15">
         <v>0</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="28.5" spans="1:12">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="22">
         <v>2</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="15">
         <v>0</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="15">
         <v>500</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="15">
         <v>1000</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="15">
         <v>200</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="15">
         <v>0</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="22">
         <v>5</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="15">
         <v>0</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="15">
         <v>0</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="15">
         <v>50</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="15">
         <v>100</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="15">
         <v>500</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="22">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="15">
         <v>0</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="15">
         <v>1000</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="15">
         <v>500</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="15">
         <v>0</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="15">
         <v>0</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="22">
         <v>2</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="15">
         <v>0</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="15">
         <v>500</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="15">
         <v>1000</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="15">
         <v>200</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="22">
         <v>4</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="15">
         <v>0</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="15">
         <v>0</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="15">
         <v>100</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="15">
         <v>200</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="15">
         <v>100</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="22">
         <v>5</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="15">
         <v>0</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="15">
         <v>50</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="15">
         <v>100</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="15">
         <v>500</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3335,268 +3490,268 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="3" width="13.75" style="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="3" width="13.75" style="10" customWidth="1"/>
+    <col min="4" max="5" width="16" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="3"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="11" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="5">
+      <c r="A9" s="14">
         <v>1</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="15" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3607,12 +3762,307 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <cols>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" ht="27" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" ht="121.5" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="27" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="1">
+        <v>100</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="1">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="1">
+        <v>50</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="3">
+        <v>100</v>
+      </c>
+      <c r="E11" s="1">
+        <v>100</v>
+      </c>
+      <c r="F11" s="2">
+        <v>100</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="1">
+        <v>100</v>
+      </c>
+      <c r="G12" s="2">
+        <v>100</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2">
+        <v>100</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2">
+        <v>100</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
